--- a/Index.xlsx
+++ b/Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sync\Research\GitHub\Peoria-Pekin_MSA_Economic_Index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99B16A86-FFB5-4BFB-BF71-5113862E0200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B5DAB7-08D1-430D-B1B0-EB7D006F019E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CFCF4985-4B32-4B5C-8483-72570DB7EFC7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="28">
   <si>
     <t>Year</t>
   </si>
@@ -175,7 +175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -184,9 +184,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC3A04A-A491-4452-82D7-3AD2F065E1A1}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
@@ -585,7 +582,7 @@
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>1</v>
       </c>
     </row>
@@ -799,10 +796,10 @@
         <v>2016</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -813,13 +810,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
@@ -828,12 +825,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>6</v>
@@ -845,63 +842,66 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>23</v>
@@ -913,12 +913,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>23</v>
@@ -930,20 +930,125 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>2011</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -967,8 +1072,8 @@
     <hyperlink ref="D11" r:id="rId16" display="https://www.bradley.edu/news-articles/fourth-quarter-2017-business-and-economic-indicators/?utm_source=chatgpt.com" xr:uid="{8D8C2C53-BBFA-4EA0-95E0-F11AAE1DB97E}"/>
     <hyperlink ref="E11" r:id="rId17" display="https://data.greaterpeoria.us/wp-content/uploads/2018/02/2017-q4-business-and-economic-indicators.pdf?utm_source=chatgpt.com" xr:uid="{84F6C9D6-E698-4119-9B1D-85B00DB47E35}"/>
     <hyperlink ref="D12" r:id="rId18" display="https://www.wglt.org/news/2017-11-28/peoria-area-economy-stable-and-slightly-up-in-third-quarter?utm_source=chatgpt.com" xr:uid="{70EE3256-2DFB-4B83-8075-15B9EA6139E3}"/>
-    <hyperlink ref="D18" r:id="rId19" display="https://www.bradley.edu/news-articles/q3-economic-indicators-released/?utm_source=chatgpt.com" xr:uid="{23055929-5983-4545-9063-F8CA6822582D}"/>
-    <hyperlink ref="D19" r:id="rId20" display="https://www.bradley.edu/news-articles/2nd-quarter-business-and-economic-indicators-released/?utm_source=chatgpt.com" xr:uid="{BA9A87BC-084F-482A-A7B2-1A9E4079D598}"/>
+    <hyperlink ref="D24" r:id="rId19" display="https://www.bradley.edu/news-articles/q3-economic-indicators-released/?utm_source=chatgpt.com" xr:uid="{23055929-5983-4545-9063-F8CA6822582D}"/>
+    <hyperlink ref="D25" r:id="rId20" display="https://www.bradley.edu/news-articles/2nd-quarter-business-and-economic-indicators-released/?utm_source=chatgpt.com" xr:uid="{BA9A87BC-084F-482A-A7B2-1A9E4079D598}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
